--- a/Catalogo_Programas.xlsx
+++ b/Catalogo_Programas.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="programas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="programas" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,6 +52,15 @@
     <font>
       <name val="Calibri"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <color rgb="00FFFFFF"/>
+      <sz val="8"/>
     </font>
   </fonts>
   <fills count="7">
@@ -113,7 +122,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -132,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -498,25 +513,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="65" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="65" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>CATÁLOGO DE PROGRAMAS — Registro Estatal de Servidores Públicos</t>
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>CATÁLOGO DE PROGRAMAS – Registro Estatal de Servidores Públicos</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">  Azul oscuro = Obligatorio  |  Datos desde fila 4  |  ID_UNIDAD debe existir en catálogo de Unidades Administrativas</t>
         </is>
@@ -525,25 +539,20 @@
     <row r="3" ht="32" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>EJERCICIO</t>
+          <t>ID_DEPCIA</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>ID_DEPCIA</t>
+          <t>ID_UNIDAD</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>ID_UNIDAD</t>
+          <t>CLAVE_PROGRAMA</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>CLAVE_PROGRAMA</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>DESCRIPCIÓN DEL PROGRAMA</t>
         </is>
@@ -552,275 +561,240 @@
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>Ej: 01</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Ej: 01</t>
+          <t>Ej: 01020201</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Ej: 01020201</t>
+          <t>Ej: E054</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Ej: E054</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
           <t>Ej: PUBLICACION OFICIAL Y LEGALIZACION DE DOCUMENTOS</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="5" t="n">
-        <v>2025</v>
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
+          <t>01020201</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>E054</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>PUBLICACION OFICIAL, LEGALIZACION DE DOCUMENTOS Y SEGUIMIENTO A LA ACTIVIDAD NOTARIAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
           <t>01</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>01020201</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>01030101</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>P014</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>INCLUSION, PARTICIPACION SOCIAL Y RELACIONES INTERINSTITUCIONALES</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>01150101</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>E052</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>REGISTRO PATRIMONIAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>01350101</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>E053</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>ACCESO A LA JUSTICIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>01360101</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>E030</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>ATENCION INTEGRAL A VICTIMAS Y OFENDIDOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>04010101</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>E037</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>SEGURIDAD PUBLICA Y PROTECCION CIUDADANA</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>07010101</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>E054</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>PUBLICACION OFICIAL, LEGALIZACION DE DOCUMENTOS Y SEGUIMIENTO A LA ACTIVIDAD NOTARIAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="6" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>01030101</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>P014</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>INCLUSION, PARTICIPACION SOCIAL Y RELACIONES INTERINSTITUCIONALES</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="5" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>01150101</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>E052</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>REGISTRO PATRIMONIAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" s="6" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>01350101</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>E053</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>ACCESO A LA JUSTICIA</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" s="5" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>01360101</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>E030</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>ATENCION INTEGRAL A VICTIMAS Y OFENDIDOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" s="6" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>04</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>04010101</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>E037</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>SEGURIDAD PUBLICA Y PROTECCION CIUDADANA</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" s="5" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>07</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>07010101</t>
-        </is>
-      </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>E054</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
           <t>EDUCACION BASICA</t>
         </is>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
-      <c r="A12" s="6" t="n">
-        <v>2025</v>
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>08010101</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>08010101</t>
+          <t>F013</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>F013</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
           <t>SERVICIOS DE SALUD</t>
         </is>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
-      <c r="A13" s="5" t="n">
-        <v>2025</v>
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>21010101</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>21010101</t>
+          <t>M001</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>M001</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
           <t>ADMINISTRACION DE RECURSOS HUMANOS</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
-      <c r="A14" s="6" t="n">
-        <v>2025</v>
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>98010101</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>98010101</t>
+          <t>O001</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>O001</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>TRANSPARENCIA Y ACCESO A LA INFORMACION</t>
         </is>
@@ -828,8 +802,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
